--- a/holdings_data.xlsx
+++ b/holdings_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11989\Desktop\TEMP\fund_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17163E05-8D15-4D28-8A72-C5E09DD1BF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED14284-594F-4386-99BE-DB6F36EB638B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29340" yWindow="1044" windowWidth="23040" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23952" yWindow="-540" windowWidth="23040" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chaochao" sheetId="1" r:id="rId1"/>
@@ -80,12 +80,6 @@
     <t>招商中证2000指数增强C</t>
   </si>
   <si>
-    <t>021378</t>
-  </si>
-  <si>
-    <t>兴业中证港股通互联网指数发起式C</t>
-  </si>
-  <si>
     <t>016814</t>
   </si>
   <si>
@@ -162,6 +156,12 @@
   </si>
   <si>
     <t>华夏恒生互联网科技业ETF联接(QDII)C</t>
+  </si>
+  <si>
+    <t>001864</t>
+  </si>
+  <si>
+    <t>中海长江三角混合</t>
   </si>
   <si>
     <t>270042</t>
@@ -276,13 +276,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -300,12 +306,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -314,7 +335,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -621,42 +644,42 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
@@ -669,7 +692,7 @@
         <v>1.2971999999999999</v>
       </c>
       <c r="E2">
-        <v>1488</v>
+        <v>1488.04</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -680,26 +703,25 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="1"/>
       <c r="K2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3">
-        <v>691.65</v>
+        <v>691.26</v>
       </c>
       <c r="D3">
-        <v>1.3886000000000001</v>
+        <v>1.3880999999999999</v>
       </c>
       <c r="E3">
-        <v>960.42</v>
+        <v>959.54</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -710,26 +732,25 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="1"/>
       <c r="K3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4">
-        <v>1290.43</v>
+        <v>1508.64</v>
       </c>
       <c r="D4">
-        <v>1.085</v>
+        <v>1.0849</v>
       </c>
       <c r="E4">
-        <v>1400.09</v>
+        <v>1636.72</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -740,26 +761,25 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="1"/>
       <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5">
-        <v>1239.83</v>
+        <v>1238.79</v>
       </c>
       <c r="D5">
         <v>1.6287</v>
       </c>
       <c r="E5">
-        <v>2019.34</v>
+        <v>2017.62</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -770,26 +790,25 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="1"/>
       <c r="K5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6">
-        <v>641.22</v>
+        <v>231.21</v>
       </c>
       <c r="D6">
-        <v>1.6674</v>
+        <v>1.73</v>
       </c>
       <c r="E6">
-        <v>1069.17</v>
+        <v>399.99</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -800,26 +819,25 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="1"/>
       <c r="K6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7">
-        <v>231.21</v>
+        <v>829.56</v>
       </c>
       <c r="D7">
-        <v>1.7301</v>
+        <v>0.65910000000000002</v>
       </c>
       <c r="E7">
-        <v>400.02</v>
+        <v>546.76</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -830,26 +848,25 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" s="1"/>
       <c r="K7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8">
-        <v>1662.6100000000001</v>
+        <v>1028.8499999999999</v>
       </c>
       <c r="D8">
-        <v>0.64339999999999997</v>
+        <v>1.3585</v>
       </c>
       <c r="E8">
-        <v>1069.72</v>
+        <v>1397.69</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -860,26 +877,25 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="1"/>
       <c r="K8">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9">
-        <v>956.97</v>
+        <v>1156.21</v>
       </c>
       <c r="D9">
-        <v>1.3585</v>
+        <v>0.75770000000000004</v>
       </c>
       <c r="E9">
-        <v>1300.07</v>
+        <v>876.06</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -890,26 +906,25 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="1"/>
       <c r="K9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10">
-        <v>1155.6500000000001</v>
+        <v>892.4</v>
       </c>
       <c r="D10">
-        <v>0.75770000000000004</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="E10">
-        <v>875.6</v>
+        <v>787.1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -920,26 +935,25 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="1"/>
       <c r="K10">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11">
-        <v>908.56</v>
+        <v>595.09</v>
       </c>
       <c r="D11">
-        <v>0.88200000000000001</v>
+        <v>1.3912</v>
       </c>
       <c r="E11">
-        <v>801.32</v>
+        <v>827.89</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -950,26 +964,25 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="1"/>
       <c r="K11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12">
-        <v>594.86</v>
+        <v>158.08000000000001</v>
       </c>
       <c r="D12">
-        <v>1.3912</v>
+        <v>1.7871999999999999</v>
       </c>
       <c r="E12">
-        <v>827.55</v>
+        <v>282.52</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -980,26 +993,25 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12" s="1"/>
       <c r="K12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13">
-        <v>160.03</v>
+        <v>451.07</v>
       </c>
       <c r="D13">
-        <v>1.7869999999999999</v>
+        <v>2.2170000000000001</v>
       </c>
       <c r="E13">
-        <v>285.95999999999998</v>
+        <v>1000.02</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1010,26 +1022,25 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="1"/>
       <c r="K13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
       </c>
       <c r="C14">
-        <v>228.49</v>
+        <v>251.74</v>
       </c>
       <c r="D14">
-        <v>2.1882999999999999</v>
+        <v>1.2121</v>
       </c>
       <c r="E14">
-        <v>500</v>
+        <v>305.13</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1040,26 +1051,25 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14" s="1"/>
       <c r="K14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15">
-        <v>259.45</v>
+        <v>203.33</v>
       </c>
       <c r="D15">
-        <v>1.2121</v>
+        <v>1.5006999999999999</v>
       </c>
       <c r="E15">
-        <v>314.48</v>
+        <v>305.14</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1070,26 +1080,25 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15" s="1"/>
       <c r="K15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>39</v>
       </c>
       <c r="B16" t="s">
         <v>40</v>
       </c>
       <c r="C16">
-        <v>209.56</v>
+        <v>772.31</v>
       </c>
       <c r="D16">
-        <v>1.5006999999999999</v>
+        <v>1.4374</v>
       </c>
       <c r="E16">
-        <v>314.48</v>
+        <v>1110.1199999999999</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1100,26 +1109,25 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="1"/>
       <c r="K16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>42</v>
       </c>
       <c r="C17">
-        <v>772.25</v>
+        <v>633.24</v>
       </c>
       <c r="D17">
-        <v>1.4374</v>
+        <v>1.5026999999999999</v>
       </c>
       <c r="E17">
-        <v>1110.01</v>
+        <v>951.57</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1130,26 +1138,25 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" s="1"/>
       <c r="K17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
       <c r="B18" t="s">
         <v>44</v>
       </c>
       <c r="C18">
-        <v>801.74</v>
+        <v>2251.42</v>
       </c>
       <c r="D18">
-        <v>1.4966999999999999</v>
+        <v>0.91420000000000001</v>
       </c>
       <c r="E18">
-        <v>1200</v>
+        <v>2058.25</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1160,26 +1167,25 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" s="1"/>
       <c r="K18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>45</v>
       </c>
       <c r="B19" t="s">
         <v>46</v>
       </c>
       <c r="C19">
-        <v>1555.23</v>
+        <v>51.76</v>
       </c>
       <c r="D19">
-        <v>0.91420000000000001</v>
+        <v>3.8639999999999999</v>
       </c>
       <c r="E19">
-        <v>1421.76</v>
+        <v>200</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1190,13 +1196,12 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="1"/>
       <c r="K19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20" t="s">
@@ -1220,13 +1225,12 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="1"/>
       <c r="K20">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1237,42 +1241,42 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>49</v>
       </c>
       <c r="B2" t="s">
@@ -1296,26 +1300,25 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="1"/>
       <c r="K2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3">
-        <v>305.67</v>
+        <v>152.83000000000001</v>
       </c>
       <c r="D3">
-        <v>1.4514</v>
+        <v>1.3703000000000001</v>
       </c>
       <c r="E3">
-        <v>443.65</v>
+        <v>209.42</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1326,17 +1329,16 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="1"/>
       <c r="K3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
+      <c r="A4" t="s">
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>1191.74</v>
@@ -1356,26 +1358,25 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="1"/>
       <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>53</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5">
-        <v>736.41</v>
+        <v>883.51</v>
       </c>
       <c r="D5">
-        <v>0.67900000000000005</v>
+        <v>0.67910000000000004</v>
       </c>
       <c r="E5">
-        <v>499.99</v>
+        <v>599.99</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1386,26 +1387,25 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="1"/>
       <c r="K5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>55</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6">
-        <v>223.23</v>
+        <v>257.87</v>
       </c>
       <c r="D6">
-        <v>2.6878000000000002</v>
+        <v>2.7145000000000001</v>
       </c>
       <c r="E6">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1416,13 +1416,12 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="1"/>
       <c r="K6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>57</v>
       </c>
       <c r="B7" t="s">
@@ -1446,13 +1445,12 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" s="1"/>
       <c r="K7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>59</v>
       </c>
       <c r="B8" t="s">
@@ -1476,13 +1474,12 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="1"/>
       <c r="K8">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>61</v>
       </c>
       <c r="B9" t="s">
@@ -1506,13 +1503,12 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="1"/>
       <c r="K9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>63</v>
       </c>
       <c r="B10" t="s">
@@ -1536,13 +1532,12 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="1"/>
       <c r="K10">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>65</v>
       </c>
       <c r="B11" t="s">
@@ -1566,26 +1561,25 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="1"/>
       <c r="K11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>67</v>
       </c>
       <c r="B12" t="s">
         <v>68</v>
       </c>
       <c r="C12">
-        <v>352.28</v>
+        <v>417.58</v>
       </c>
       <c r="D12">
-        <v>1.4194</v>
+        <v>1.4369000000000001</v>
       </c>
       <c r="E12">
-        <v>500.01</v>
+        <v>600.01</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1596,26 +1590,25 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12" s="1"/>
       <c r="K12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>69</v>
       </c>
       <c r="B13" t="s">
         <v>70</v>
       </c>
       <c r="C13">
-        <v>359.89</v>
+        <v>433.51</v>
       </c>
       <c r="D13">
-        <v>1.3894</v>
+        <v>1.3841000000000001</v>
       </c>
       <c r="E13">
-        <v>500.01</v>
+        <v>600.01</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1626,26 +1619,25 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="1"/>
       <c r="K13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>71</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14">
-        <v>89.93</v>
+        <v>175.35</v>
       </c>
       <c r="D14">
-        <v>1.1120000000000001</v>
+        <v>1.1406000000000001</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1656,13 +1648,12 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14" s="1"/>
       <c r="K14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>73</v>
       </c>
       <c r="B15" t="s">
@@ -1686,26 +1677,25 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15" s="1"/>
       <c r="K15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>75</v>
       </c>
       <c r="B16" t="s">
         <v>76</v>
       </c>
       <c r="C16">
-        <v>154.96</v>
+        <v>233.77</v>
       </c>
       <c r="D16">
-        <v>1.2907</v>
+        <v>1.2833000000000001</v>
       </c>
       <c r="E16">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1716,13 +1706,12 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="1"/>
       <c r="K16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>77</v>
       </c>
       <c r="B17" t="s">
@@ -1746,13 +1735,12 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" s="1"/>
       <c r="K17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>79</v>
       </c>
       <c r="B18" t="s">
@@ -1776,13 +1764,12 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" s="1"/>
       <c r="K18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>81</v>
       </c>
       <c r="B19" t="s">
@@ -1806,13 +1793,12 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="1"/>
       <c r="K19">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/holdings_data.xlsx
+++ b/holdings_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1952.85</v>
+        <v>3581.32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9196</v>
+        <v>0.8923</v>
       </c>
       <c r="E2" t="n">
-        <v>1795.83</v>
+        <v>3195.75</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -524,22 +524,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>015401</t>
+          <t>008987</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>弘毅远方甄选混合C</t>
+          <t>广发上海金ETF联接C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1133.4</v>
+        <v>1186</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4227</v>
+        <v>2.0283</v>
       </c>
       <c r="E3" t="n">
-        <v>1612.5</v>
+        <v>2405.52</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -559,22 +559,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>025165</t>
+          <t>015401</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>易方达创业板增强C</t>
+          <t>弘毅远方甄选混合C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1493.98</v>
+        <v>1296.93</v>
       </c>
       <c r="D4" t="n">
-        <v>0.987</v>
+        <v>1.3974</v>
       </c>
       <c r="E4" t="n">
-        <v>1474.53</v>
+        <v>1812.37</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1121.09</v>
+        <v>1455.59</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0534</v>
+        <v>1.0794</v>
       </c>
       <c r="E5" t="n">
-        <v>1180.94</v>
+        <v>1571.16</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -629,22 +629,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>008987</t>
+          <t>016582</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>广发上海金ETF联接C</t>
+          <t>嘉实上海金ETF发起联接C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>557.58</v>
+        <v>729.37</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0739</v>
+        <v>1.9195</v>
       </c>
       <c r="E6" t="n">
-        <v>1156.36</v>
+        <v>1400.03</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -664,22 +664,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>018388</t>
+          <t>001864</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>华泰柏瑞港股通红利ETF联接基金C</t>
+          <t>中海魅力长三角混合</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>689.4400000000001</v>
+        <v>385.92</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3984</v>
+        <v>3.6223</v>
       </c>
       <c r="E7" t="n">
-        <v>964.11</v>
+        <v>1397.92</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -699,22 +699,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>001864</t>
+          <t>012920</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中海魅力长三角混合</t>
+          <t>易方达全球成长精选混合(QDII)人民币A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>239.54</v>
+        <v>559.17</v>
       </c>
       <c r="D8" t="n">
-        <v>3.7447</v>
+        <v>2.3317</v>
       </c>
       <c r="E8" t="n">
-        <v>897.02</v>
+        <v>1303.82</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -734,22 +734,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>017223</t>
+          <t>025165</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富国中证电池主题ETF发起式联接C</t>
+          <t>易方达创业板增强C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>848.34</v>
+        <v>1269.69</v>
       </c>
       <c r="D9" t="n">
-        <v>0.995</v>
+        <v>0.9657</v>
       </c>
       <c r="E9" t="n">
-        <v>844.1</v>
+        <v>1226.18</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>012920</t>
+          <t>016008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>易方达全球成长精选混合(QDII)人民币A</t>
+          <t>招商中证消费电子主题ETF联接C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>356.76</v>
+        <v>758</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2531</v>
+        <v>1.5831</v>
       </c>
       <c r="E10" t="n">
-        <v>803.8200000000001</v>
+        <v>1200.01</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -804,22 +804,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>270042</t>
+          <t>018388</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>广发纳斯达克100ETF联接人民币(QDII)A</t>
+          <t>华泰柏瑞港股通红利ETF联接基金C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>107.98</v>
+        <v>825.7</v>
       </c>
       <c r="D11" t="n">
-        <v>7.1695</v>
+        <v>1.4057</v>
       </c>
       <c r="E11" t="n">
-        <v>774.16</v>
+        <v>1160.68</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -839,22 +839,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>017647</t>
+          <t>013180</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>易方达中证光伏产业ETF联接发起式C</t>
+          <t>广发国证新能源车电池ETF联接C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>700.9400000000001</v>
+        <v>1144.18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7151</v>
+        <v>0.8711</v>
       </c>
       <c r="E12" t="n">
-        <v>501.24</v>
+        <v>996.75</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -874,22 +874,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>017227</t>
+          <t>023482</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>富国中证全指家用电器ETF发起式联接C</t>
+          <t>万家中证港股通创新药ETF发起式联接C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>296.59</v>
+        <v>614.54</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4809</v>
+        <v>1.4672</v>
       </c>
       <c r="E13" t="n">
-        <v>439.22</v>
+        <v>901.6799999999999</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -909,22 +909,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>020671</t>
+          <t>024663</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>易方达上证科创板芯片指数发起式C</t>
+          <t>富国创业板人工智能ETF发起式联接C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>117.38</v>
+        <v>436.74</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2789</v>
+        <v>1.3738</v>
       </c>
       <c r="E14" t="n">
-        <v>267.5</v>
+        <v>599.99</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -944,22 +944,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>020412</t>
+          <t>270042</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>永赢中证沪深港黄金产业股票ETF发起联接C</t>
+          <t>广发纳斯达克100ETF联接人民币(QDII)A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53.51</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6106</v>
+        <v>7.0203</v>
       </c>
       <c r="E15" t="n">
-        <v>139.69</v>
+        <v>561.62</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -979,22 +979,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>019671</t>
+          <t>025194</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>广发港股创新药ETF联接(QDII)C</t>
+          <t>银华中证全指证券公司ETF发起式联接C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>69.58</v>
+        <v>517.76</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5631</v>
+        <v>0.9657</v>
       </c>
       <c r="E16" t="n">
-        <v>108.76</v>
+        <v>500</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1014,22 +1014,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>020900</t>
+          <t>015897</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>天弘中证全指通信设备指数发起C</t>
+          <t>天弘中证细分化工产业主题ETF联接C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>48.58</v>
+        <v>603.45</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5369</v>
+        <v>0.8286</v>
       </c>
       <c r="E17" t="n">
-        <v>74.66</v>
+        <v>500</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1043,6 +1043,321 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>017647</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>易方达中证光伏产业ETF联接发起式C</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>642.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7762</v>
+      </c>
+      <c r="E18" t="n">
+        <v>498.49</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>017227</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>富国中证全指家用电器ETF发起式联接C</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>296.59</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.4809</v>
+      </c>
+      <c r="E19" t="n">
+        <v>439.22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>023896</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>天弘上证科创板综合指数增强C</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>281.93</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.4188</v>
+      </c>
+      <c r="E20" t="n">
+        <v>400</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>020671</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>易方达上证科创板芯片指数发起式C</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>176.72</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.2635</v>
+      </c>
+      <c r="E21" t="n">
+        <v>400</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>025209</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>永赢先锋半导体智选混合发起C</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>221.24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.3403</v>
+      </c>
+      <c r="E22" t="n">
+        <v>296.52</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>023887</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>永赢北证50成份指数发起C</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>244.12</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.1105</v>
+      </c>
+      <c r="E23" t="n">
+        <v>271.09</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>290014</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>泰信现代服务业混合</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>88.26000000000001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.266</v>
+      </c>
+      <c r="E24" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>023829</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>万家中证半导体材料设备主题ETF发起式联接C</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>144.19</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.3871</v>
+      </c>
+      <c r="E25" t="n">
+        <v>200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>022486</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>国金中证A500指数增强C</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>152.74</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.3094</v>
+      </c>
+      <c r="E26" t="n">
+        <v>200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1057,7 +1372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,13 +1444,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1478.8</v>
+        <v>1629.13</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2848</v>
+        <v>1.289</v>
       </c>
       <c r="E2" t="n">
-        <v>1899.96</v>
+        <v>2099.96</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1155,22 +1470,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>007280</t>
+          <t>020608</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>摩根日本精选股票(QDII)A</t>
+          <t>南方中证机器人ETF发起联接C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>657.99</v>
+        <v>844.2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8237</v>
+        <v>1.4215</v>
       </c>
       <c r="E3" t="n">
-        <v>1199.98</v>
+        <v>1200.01</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1190,22 +1505,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>000834</t>
+          <t>007280</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大成纳斯达克100ETF联接(QDII)A</t>
+          <t>摩根日本精选股票(QDII)A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>216.33</v>
+        <v>657.99</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0848</v>
+        <v>1.8237</v>
       </c>
       <c r="E4" t="n">
-        <v>1099.99</v>
+        <v>1199.98</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1225,22 +1540,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>020608</t>
+          <t>013309</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南方中证机器人ETF发起联接C</t>
+          <t>易方达恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>699.48</v>
+        <v>775.54</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4296</v>
+        <v>1.4184</v>
       </c>
       <c r="E5" t="n">
-        <v>1000.01</v>
+        <v>1100</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1260,22 +1575,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>021172</t>
+          <t>000834</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华安北证50成份指数发起式A</t>
+          <t>大成纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>487.05</v>
+        <v>216.33</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9847</v>
+        <v>5.0848</v>
       </c>
       <c r="E6" t="n">
-        <v>966.65</v>
+        <v>1099.99</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1295,22 +1610,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>012060</t>
+          <t>004070</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>富国全球消费精选混合(QDII)人民币A</t>
+          <t>南方中证全指证券公司ETF联接C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>561.84</v>
+        <v>770.63</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6019</v>
+        <v>1.2899</v>
       </c>
       <c r="E7" t="n">
-        <v>900.01</v>
+        <v>994.02</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1330,22 +1645,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>013416</t>
+          <t>021172</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>永赢中证全指医疗器械ETF发起联接C</t>
+          <t>华安北证50成份指数发起式A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1182.85</v>
+        <v>487.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6764</v>
+        <v>1.9847</v>
       </c>
       <c r="E8" t="n">
-        <v>800.02</v>
+        <v>966.65</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1365,22 +1680,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>004070</t>
+          <t>013416</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南方中证全指证券公司ETF联接C</t>
+          <t>永赢中证全指医疗器械ETF发起联接C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>613.52</v>
+        <v>1336.96</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2942</v>
+        <v>0.6732</v>
       </c>
       <c r="E9" t="n">
-        <v>794.02</v>
+        <v>900.02</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1400,22 +1715,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>019671</t>
+          <t>012060</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>广发港股创新药ETF联接(QDII)C</t>
+          <t>富国全球消费精选混合(QDII)人民币A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>449.88</v>
+        <v>561.84</v>
       </c>
       <c r="D10" t="n">
-        <v>1.556</v>
+        <v>1.6019</v>
       </c>
       <c r="E10" t="n">
-        <v>700.01</v>
+        <v>900.01</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1435,19 +1750,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>002834</t>
+          <t>019671</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华夏新锦绣混合C</t>
+          <t>广发港股创新药ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>258.42</v>
+        <v>449.88</v>
       </c>
       <c r="D11" t="n">
-        <v>2.7088</v>
+        <v>1.556</v>
       </c>
       <c r="E11" t="n">
         <v>700.01</v>
@@ -1470,22 +1785,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>024195</t>
+          <t>002834</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>永赢国证商用卫星通信产业ETF发起联接C</t>
+          <t>华夏新锦绣混合C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>523.6</v>
+        <v>258.42</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1459</v>
+        <v>2.7088</v>
       </c>
       <c r="E12" t="n">
-        <v>600.01</v>
+        <v>700.01</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1505,22 +1820,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012725</t>
+          <t>024195</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>国泰中证畜牧养殖ETF联接C</t>
+          <t>永赢国证商用卫星通信产业ETF发起联接C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>509.16</v>
+        <v>523.6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7856</v>
+        <v>1.1459</v>
       </c>
       <c r="E13" t="n">
-        <v>400</v>
+        <v>600.01</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1540,22 +1855,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>018647</t>
+          <t>025209</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>易方达中证家电龙头ETF联接发起式C</t>
+          <t>永赢先锋半导体智选混合发起C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>301.25</v>
+        <v>374.72</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3278</v>
+        <v>1.3343</v>
       </c>
       <c r="E14" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1575,22 +1890,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>013309</t>
+          <t>018897</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>易方达恒生科技ETF联接(QDII)C</t>
+          <t>易方达消费电子ETF联接C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>274.95</v>
+        <v>251.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4548</v>
+        <v>1.8463</v>
       </c>
       <c r="E15" t="n">
-        <v>400</v>
+        <v>465.18</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1610,22 +1925,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>018897</t>
+          <t>012725</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>易方达消费电子ETF联接C</t>
+          <t>国泰中证畜牧养殖ETF联接C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>142.29</v>
+        <v>509.16</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8637</v>
+        <v>0.7856</v>
       </c>
       <c r="E16" t="n">
-        <v>265.18</v>
+        <v>400</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1645,22 +1960,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>004744</t>
+          <t>018647</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>易方达创业板ETF联接C</t>
+          <t>易方达中证家电龙头ETF联接发起式C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>86.97</v>
+        <v>301.25</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0426</v>
+        <v>1.3278</v>
       </c>
       <c r="E17" t="n">
-        <v>264.61</v>
+        <v>400</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1674,6 +1989,181 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>012769</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>华夏中证动漫游戏ETF发起式联接C</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>199.39</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.5046</v>
+      </c>
+      <c r="E18" t="n">
+        <v>300</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>015945</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>易方达国防军工混合C</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>204.12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.4697</v>
+      </c>
+      <c r="E19" t="n">
+        <v>300</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>020900</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>天弘中证全指通信设备指数发起C</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.2799</v>
+      </c>
+      <c r="E20" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>015897</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>天弘中证细分化工产业主题ETF联接C</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>121.45</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8234</v>
+      </c>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>021959</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>南方中证沪深港黄金产业股票指数发起C</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.5919</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
     </row>

--- a/holdings_data.xlsx
+++ b/holdings_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,22 +489,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>013172</t>
+          <t>008987</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>华夏恒生互联网科技业ETF联接(QDII)C</t>
+          <t>广发上海金ETF联接C</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3581.32</v>
+        <v>1660.89</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8923</v>
+        <v>2.0087</v>
       </c>
       <c r="E2" t="n">
-        <v>3195.75</v>
+        <v>3336.21</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -524,22 +524,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>008987</t>
+          <t>013172</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>广发上海金ETF联接C</t>
+          <t>华夏恒生互联网科技业ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1186</v>
+        <v>3271.87</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0283</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2405.52</v>
+        <v>2930.61</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -559,22 +559,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>015401</t>
+          <t>017647</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>弘毅远方甄选混合C</t>
+          <t>易方达中证光伏产业ETF联接发起式C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1296.93</v>
+        <v>2855.73</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3974</v>
+        <v>0.7348</v>
       </c>
       <c r="E4" t="n">
-        <v>1812.37</v>
+        <v>2098.39</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -594,22 +594,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>022435</t>
+          <t>013180</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南方中证A500ETF联接C</t>
+          <t>广发国证新能源车电池ETF联接C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1455.59</v>
+        <v>2428.32</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0794</v>
+        <v>0.8439</v>
       </c>
       <c r="E5" t="n">
-        <v>1571.16</v>
+        <v>2049.2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -629,22 +629,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>016582</t>
+          <t>025446</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>嘉实上海金ETF发起联接C</t>
+          <t>万家周期视野股票发起式C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>729.37</v>
+        <v>2042.21</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9195</v>
+        <v>0.9937</v>
       </c>
       <c r="E6" t="n">
-        <v>1400.03</v>
+        <v>2029.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -664,22 +664,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>001864</t>
+          <t>015401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中海魅力长三角混合</t>
+          <t>弘毅远方甄选混合C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>385.92</v>
+        <v>1322.89</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6223</v>
+        <v>1.4128</v>
       </c>
       <c r="E7" t="n">
-        <v>1397.92</v>
+        <v>1868.98</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -699,22 +699,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>012920</t>
+          <t>022486</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>易方达全球成长精选混合(QDII)人民币A</t>
+          <t>国金中证A500指数增强C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>559.17</v>
+        <v>1411.76</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3317</v>
+        <v>1.273</v>
       </c>
       <c r="E8" t="n">
-        <v>1303.82</v>
+        <v>1797.16</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -734,22 +734,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>025165</t>
+          <t>001864</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>易方达创业板增强C</t>
+          <t>中海魅力长三角混合</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1269.69</v>
+        <v>469.25</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9657</v>
+        <v>3.6149</v>
       </c>
       <c r="E9" t="n">
-        <v>1226.18</v>
+        <v>1696.27</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>016008</t>
+          <t>020671</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>招商中证消费电子主题ETF联接C</t>
+          <t>易方达上证科创板芯片指数发起式C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>758</v>
+        <v>618.45</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5831</v>
+        <v>2.2637</v>
       </c>
       <c r="E10" t="n">
-        <v>1200.01</v>
+        <v>1399.98</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -804,22 +804,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>018388</t>
+          <t>012920</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华泰柏瑞港股通红利ETF联接基金C</t>
+          <t>易方达全球成长精选混合(QDII)人民币A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>825.7</v>
+        <v>559.17</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4057</v>
+        <v>2.3317</v>
       </c>
       <c r="E11" t="n">
-        <v>1160.68</v>
+        <v>1303.82</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -839,22 +839,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>013180</t>
+          <t>020902</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>广发国证新能源车电池ETF联接C</t>
+          <t>招商成长量化选股股票C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1144.18</v>
+        <v>878.34</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8711</v>
+        <v>1.4801</v>
       </c>
       <c r="E12" t="n">
-        <v>996.75</v>
+        <v>1300.03</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -874,22 +874,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>023482</t>
+          <t>015897</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>万家中证港股通创新药ETF发起式联接C</t>
+          <t>天弘中证细分化工产业主题ETF联接C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>614.54</v>
+        <v>1605.09</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4672</v>
+        <v>0.8099</v>
       </c>
       <c r="E13" t="n">
-        <v>901.6799999999999</v>
+        <v>1300</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -909,22 +909,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>024663</t>
+          <t>023482</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富国创业板人工智能ETF发起式联接C</t>
+          <t>万家中证港股通创新药ETF发起式联接C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>436.74</v>
+        <v>899.5599999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3738</v>
+        <v>1.4451</v>
       </c>
       <c r="E14" t="n">
-        <v>599.99</v>
+        <v>1299.98</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -944,22 +944,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>270042</t>
+          <t>023829</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>广发纳斯达克100ETF联接人民币(QDII)A</t>
+          <t>万家中证半导体材料设备主题ETF发起式联接C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>744.65</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0203</v>
+        <v>1.3167</v>
       </c>
       <c r="E15" t="n">
-        <v>561.62</v>
+        <v>980.51</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>517.76</v>
+        <v>942.98</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9657</v>
+        <v>0.9545</v>
       </c>
       <c r="E16" t="n">
-        <v>500</v>
+        <v>900.04</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1014,22 +1014,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>015897</t>
+          <t>270042</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>天弘中证细分化工产业主题ETF联接C</t>
+          <t>广发纳斯达克100ETF联接人民币(QDII)A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>603.45</v>
+        <v>99.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8286</v>
+        <v>7.0674</v>
       </c>
       <c r="E17" t="n">
-        <v>500</v>
+        <v>701.09</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>017647</t>
+          <t>002833</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>易方达中证光伏产业ETF联接发起式C</t>
+          <t>华夏新锦绣混合A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>642.2</v>
+        <v>232.64</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7762</v>
+        <v>3.0092</v>
       </c>
       <c r="E18" t="n">
-        <v>498.49</v>
+        <v>700.0599999999999</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1084,22 +1084,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>017227</t>
+          <t>013309</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富国中证全指家用电器ETF发起式联接C</t>
+          <t>易方达恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>296.59</v>
+        <v>296.41</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4809</v>
+        <v>1.3495</v>
       </c>
       <c r="E19" t="n">
-        <v>439.22</v>
+        <v>400</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>023896</t>
+          <t>025165</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>天弘上证科创板综合指数增强C</t>
+          <t>易方达创业板增强C</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>281.93</v>
+        <v>408.27</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4188</v>
+        <v>0.9034</v>
       </c>
       <c r="E20" t="n">
-        <v>400</v>
+        <v>368.85</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1154,22 +1154,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>020671</t>
+          <t>022365</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>易方达上证科创板芯片指数发起式C</t>
+          <t>永赢科技智选混合发起C</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>176.72</v>
+        <v>114.11</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2635</v>
+        <v>3.1367</v>
       </c>
       <c r="E21" t="n">
-        <v>400</v>
+        <v>357.93</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1183,181 +1183,6 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>025209</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>永赢先锋半导体智选混合发起C</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>221.24</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.3403</v>
-      </c>
-      <c r="E22" t="n">
-        <v>296.52</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>023887</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>永赢北证50成份指数发起C</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>244.12</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.1105</v>
-      </c>
-      <c r="E23" t="n">
-        <v>271.09</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>290014</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>泰信现代服务业混合</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>88.26000000000001</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.266</v>
-      </c>
-      <c r="E24" t="n">
-        <v>200</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>023829</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>万家中证半导体材料设备主题ETF发起式联接C</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>144.19</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.3871</v>
-      </c>
-      <c r="E25" t="n">
-        <v>200</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>022486</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>国金中证A500指数增强C</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>152.74</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.3094</v>
-      </c>
-      <c r="E26" t="n">
-        <v>200</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1372,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1435,22 +1260,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>021457</t>
+          <t>019671</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>易方达恒生红利低波ETF联接A</t>
+          <t>广发港股创新药ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1629.13</v>
+        <v>1504.49</v>
       </c>
       <c r="D2" t="n">
-        <v>1.289</v>
+        <v>1.4623</v>
       </c>
       <c r="E2" t="n">
-        <v>2099.96</v>
+        <v>2200.02</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1479,13 +1304,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>844.2</v>
+        <v>1068.45</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4215</v>
+        <v>1.4039</v>
       </c>
       <c r="E3" t="n">
-        <v>1200.01</v>
+        <v>1500.02</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1505,22 +1330,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>007280</t>
+          <t>013309</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>摩根日本精选股票(QDII)A</t>
+          <t>易方达恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>657.99</v>
+        <v>1062.61</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8237</v>
+        <v>1.4116</v>
       </c>
       <c r="E4" t="n">
-        <v>1199.98</v>
+        <v>1500.01</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1540,22 +1365,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>013309</t>
+          <t>004070</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>易方达恒生科技ETF联接(QDII)C</t>
+          <t>南方中证全指证券公司ETF联接C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>775.54</v>
+        <v>1010.58</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4184</v>
+        <v>1.2805</v>
       </c>
       <c r="E5" t="n">
-        <v>1100</v>
+        <v>1294.04</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1575,22 +1400,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>000834</t>
+          <t>021172</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大成纳斯达克100ETF联接(QDII)A</t>
+          <t>华安北证50成份指数发起式A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>216.33</v>
+        <v>592.5599999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>5.0848</v>
+        <v>1.9688</v>
       </c>
       <c r="E6" t="n">
-        <v>1099.99</v>
+        <v>1166.66</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1610,22 +1435,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>004070</t>
+          <t>021457</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南方中证全指证券公司ETF联接C</t>
+          <t>易方达恒生红利低波ETF联接A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>770.63</v>
+        <v>814.51</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2899</v>
+        <v>1.2891</v>
       </c>
       <c r="E7" t="n">
-        <v>994.02</v>
+        <v>1049.98</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1645,22 +1470,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>021172</t>
+          <t>013416</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>华安北证50成份指数发起式A</t>
+          <t>永赢中证全指医疗器械ETF发起联接C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>487.05</v>
+        <v>1339.1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9847</v>
+        <v>0.6721</v>
       </c>
       <c r="E8" t="n">
-        <v>966.65</v>
+        <v>900.01</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1680,22 +1505,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>013416</t>
+          <t>012060</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>永赢中证全指医疗器械ETF发起联接C</t>
+          <t>富国全球消费精选混合(QDII)人民币A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1336.96</v>
+        <v>561.84</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6732</v>
+        <v>1.6019</v>
       </c>
       <c r="E9" t="n">
-        <v>900.02</v>
+        <v>900.01</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1715,22 +1540,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>012060</t>
+          <t>025209</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富国全球消费精选混合(QDII)人民币A</t>
+          <t>永赢先锋半导体智选混合发起C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>561.84</v>
+        <v>529.4400000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6019</v>
+        <v>1.3222</v>
       </c>
       <c r="E10" t="n">
-        <v>900.01</v>
+        <v>700.02</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1750,22 +1575,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>019671</t>
+          <t>012769</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>广发港股创新药ETF联接(QDII)C</t>
+          <t>华夏中证动漫游戏ETF发起式联接C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>449.88</v>
+        <v>472.84</v>
       </c>
       <c r="D11" t="n">
-        <v>1.556</v>
+        <v>1.4804</v>
       </c>
       <c r="E11" t="n">
-        <v>700.01</v>
+        <v>699.99</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1785,22 +1610,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>002834</t>
+          <t>007280</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>华夏新锦绣混合C</t>
+          <t>摩根日本精选股票(QDII)A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>258.42</v>
+        <v>380.65</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7088</v>
+        <v>1.8389</v>
       </c>
       <c r="E12" t="n">
-        <v>700.01</v>
+        <v>699.98</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1820,22 +1645,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>024195</t>
+          <t>012725</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>永赢国证商用卫星通信产业ETF发起联接C</t>
+          <t>国泰中证畜牧养殖ETF联接C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>523.6</v>
+        <v>766.29</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1459</v>
+        <v>0.783</v>
       </c>
       <c r="E13" t="n">
-        <v>600.01</v>
+        <v>600.03</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1855,22 +1680,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>025209</t>
+          <t>018897</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>永赢先锋半导体智选混合发起C</t>
+          <t>易方达消费电子ETF联接C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>374.72</v>
+        <v>312.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3343</v>
+        <v>1.8127</v>
       </c>
       <c r="E14" t="n">
-        <v>500</v>
+        <v>566.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1890,22 +1715,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>018897</t>
+          <t>015945</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>易方达消费电子ETF联接C</t>
+          <t>易方达国防军工混合C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>251.95</v>
+        <v>274.04</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8463</v>
+        <v>1.4596</v>
       </c>
       <c r="E15" t="n">
-        <v>465.18</v>
+        <v>399.99</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1925,22 +1750,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>012725</t>
+          <t>015897</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>国泰中证畜牧养殖ETF联接C</t>
+          <t>天弘中证细分化工产业主题ETF联接C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>509.16</v>
+        <v>375.32</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7856</v>
+        <v>0.7993</v>
       </c>
       <c r="E16" t="n">
-        <v>400</v>
+        <v>300.01</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1960,22 +1785,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>018647</t>
+          <t>011103</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>易方达中证家电龙头ETF联接发起式C</t>
+          <t>天弘中证光伏产业指数C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>301.25</v>
+        <v>248.92</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3278</v>
+        <v>0.8035</v>
       </c>
       <c r="E17" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1995,22 +1820,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>012769</t>
+          <t>000834</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>华夏中证动漫游戏ETF发起式联接C</t>
+          <t>大成纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>199.39</v>
+        <v>17.66</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5046</v>
+        <v>5.3473</v>
       </c>
       <c r="E18" t="n">
-        <v>300</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2024,146 +1849,6 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>015945</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>易方达国防军工混合C</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>204.12</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.4697</v>
-      </c>
-      <c r="E19" t="n">
-        <v>300</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>020900</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>天弘中证全指通信设备指数发起C</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>87.72</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.2799</v>
-      </c>
-      <c r="E20" t="n">
-        <v>200</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>015897</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>天弘中证细分化工产业主题ETF联接C</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>121.45</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8234</v>
-      </c>
-      <c r="E21" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>021959</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>南方中证沪深港黄金产业股票指数发起C</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>62.82</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.5919</v>
-      </c>
-      <c r="E22" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
         <v>1</v>
       </c>
     </row>

--- a/holdings_data.xlsx
+++ b/holdings_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,22 +489,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>008987</t>
+          <t>015897</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>广发上海金ETF联接C</t>
+          <t>天弘中证细分化工产业主题ETF联接C</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1660.89</v>
+        <v>5627.48</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0087</v>
+        <v>1.015</v>
       </c>
       <c r="E2" t="n">
-        <v>3336.21</v>
+        <v>5711.95</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -524,22 +524,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>013172</t>
+          <t>009883</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>华夏恒生互联网科技业ETF联接(QDII)C</t>
+          <t>华润元大核心动力混合C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3271.87</v>
+        <v>4145.25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.2062</v>
       </c>
       <c r="E3" t="n">
-        <v>2930.61</v>
+        <v>5000</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -559,22 +559,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>017647</t>
+          <t>021536</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>易方达中证光伏产业ETF联接发起式C</t>
+          <t>天弘中证软件服务指数发起C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2855.73</v>
+        <v>2257.84</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7348</v>
+        <v>1.6774</v>
       </c>
       <c r="E4" t="n">
-        <v>2098.39</v>
+        <v>3787.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -594,22 +594,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>013180</t>
+          <t>015401</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>广发国证新能源车电池ETF联接C</t>
+          <t>弘毅远方甄选混合C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2428.32</v>
+        <v>2784.14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8439</v>
+        <v>1.3355</v>
       </c>
       <c r="E5" t="n">
-        <v>2049.2</v>
+        <v>3718.09</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -629,22 +629,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>025446</t>
+          <t>013172</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>万家周期视野股票发起式C</t>
+          <t>华夏恒生互联网科技业ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2042.21</v>
+        <v>4194.31</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9937</v>
+        <v>0.8578</v>
       </c>
       <c r="E6" t="n">
-        <v>2029.3</v>
+        <v>3597.87</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -664,22 +664,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>015401</t>
+          <t>013180</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>弘毅远方甄选混合C</t>
+          <t>广发国证新能源车电池ETF联接C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1322.89</v>
+        <v>2602.12</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4128</v>
+        <v>0.7985</v>
       </c>
       <c r="E7" t="n">
-        <v>1868.98</v>
+        <v>2077.88</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -699,22 +699,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>022486</t>
+          <t>023852</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>国金中证A500指数增强C</t>
+          <t>富国上证科创板新能源ETF发起式联接C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1411.76</v>
+        <v>1109.78</v>
       </c>
       <c r="D8" t="n">
-        <v>1.273</v>
+        <v>1.6489</v>
       </c>
       <c r="E8" t="n">
-        <v>1797.16</v>
+        <v>1829.86</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -734,22 +734,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>001864</t>
+          <t>015790</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中海魅力长三角混合</t>
+          <t>永赢高端装备智选混合发起C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>469.25</v>
+        <v>632.11</v>
       </c>
       <c r="D9" t="n">
-        <v>3.6149</v>
+        <v>1.582</v>
       </c>
       <c r="E9" t="n">
-        <v>1696.27</v>
+        <v>1000</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>020671</t>
+          <t>023881</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>易方达上证科创板芯片指数发起式C</t>
+          <t>兴全商业模式混合(LOF)C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>618.45</v>
+        <v>99.52</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2637</v>
+        <v>5.024</v>
       </c>
       <c r="E10" t="n">
-        <v>1399.98</v>
+        <v>500</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -804,22 +804,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>012920</t>
+          <t>024663</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>易方达全球成长精选混合(QDII)人民币A</t>
+          <t>富国创业板人工智能ETF发起式联接C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>559.17</v>
+        <v>292.43</v>
       </c>
       <c r="D11" t="n">
-        <v>2.3317</v>
+        <v>1.7098</v>
       </c>
       <c r="E11" t="n">
-        <v>1303.82</v>
+        <v>500</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -839,22 +839,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>020902</t>
+          <t>025209</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>招商成长量化选股股票C</t>
+          <t>永赢先锋半导体智选混合发起C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>878.34</v>
+        <v>301.13</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4801</v>
+        <v>1.6604</v>
       </c>
       <c r="E12" t="n">
-        <v>1300.03</v>
+        <v>500</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -874,22 +874,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>015897</t>
+          <t>025857</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>天弘中证细分化工产业主题ETF联接C</t>
+          <t>华夏中证电网设备主题ETF发起式联接C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1605.09</v>
+        <v>302.07</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8099</v>
+        <v>1.3242</v>
       </c>
       <c r="E13" t="n">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -909,22 +909,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>023482</t>
+          <t>012414</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>万家中证港股通创新药ETF发起式联接C</t>
+          <t>招商中证白酒指数(LOF)C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>899.5599999999999</v>
+        <v>277.68</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4451</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1299.98</v>
+        <v>200</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -938,251 +938,6 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>023829</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>万家中证半导体材料设备主题ETF发起式联接C</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>744.65</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.3167</v>
-      </c>
-      <c r="E15" t="n">
-        <v>980.51</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>025194</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>银华中证全指证券公司ETF发起式联接C</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>942.98</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.9545</v>
-      </c>
-      <c r="E16" t="n">
-        <v>900.04</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>270042</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>广发纳斯达克100ETF联接人民币(QDII)A</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>7.0674</v>
-      </c>
-      <c r="E17" t="n">
-        <v>701.09</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>002833</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>华夏新锦绣混合A</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>232.64</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.0092</v>
-      </c>
-      <c r="E18" t="n">
-        <v>700.0599999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>013309</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>易方达恒生科技ETF联接(QDII)C</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>296.41</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.3495</v>
-      </c>
-      <c r="E19" t="n">
-        <v>400</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>025165</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>易方达创业板增强C</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>408.27</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.9034</v>
-      </c>
-      <c r="E20" t="n">
-        <v>368.85</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>022365</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>永赢科技智选混合发起C</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>114.11</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.1367</v>
-      </c>
-      <c r="E21" t="n">
-        <v>357.93</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1197,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1260,22 +1015,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>019671</t>
+          <t>013309</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>广发港股创新药ETF联接(QDII)C</t>
+          <t>易方达恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1504.49</v>
+        <v>1953.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4623</v>
+        <v>1.3449</v>
       </c>
       <c r="E2" t="n">
-        <v>2200.02</v>
+        <v>2627.71</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1295,22 +1050,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>020608</t>
+          <t>023754</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南方中证机器人ETF发起联接C</t>
+          <t>永赢信息产业智选混合发起C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1068.45</v>
+        <v>2248.37</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4039</v>
+        <v>1.0669</v>
       </c>
       <c r="E3" t="n">
-        <v>1500.02</v>
+        <v>2398.86</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1330,22 +1085,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>013309</t>
+          <t>004070</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>易方达恒生科技ETF联接(QDII)C</t>
+          <t>南方中证全指证券公司ETF联接C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1062.61</v>
+        <v>1578.92</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4116</v>
+        <v>1.2624</v>
       </c>
       <c r="E4" t="n">
-        <v>1500.01</v>
+        <v>1993.24</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1365,22 +1120,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>004070</t>
+          <t>012725</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南方中证全指证券公司ETF联接C</t>
+          <t>国泰中证畜牧养殖ETF联接C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1010.58</v>
+        <v>2193.29</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2805</v>
+        <v>0.7751</v>
       </c>
       <c r="E5" t="n">
-        <v>1294.04</v>
+        <v>1700.03</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1400,22 +1155,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>021172</t>
+          <t>013416</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华安北证50成份指数发起式A</t>
+          <t>永赢中证全指医疗器械ETF发起联接C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>592.5599999999999</v>
+        <v>2597.91</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9688</v>
+        <v>0.6505</v>
       </c>
       <c r="E6" t="n">
-        <v>1166.66</v>
+        <v>1689.87</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1435,22 +1190,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>021457</t>
+          <t>024738</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>易方达恒生红利低波ETF联接A</t>
+          <t>永赢新材料智选混合发起C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>814.51</v>
+        <v>1088.19</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2891</v>
+        <v>1.1946</v>
       </c>
       <c r="E7" t="n">
-        <v>1049.98</v>
+        <v>1300</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1470,22 +1225,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>013416</t>
+          <t>016550</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>永赢中证全指医疗器械ETF发起联接C</t>
+          <t>永赢消费龙头智选混合发起C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1339.1</v>
+        <v>807.0599999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6721</v>
+        <v>0.9913</v>
       </c>
       <c r="E8" t="n">
-        <v>900.01</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1505,22 +1260,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>012060</t>
+          <t>018647</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富国全球消费精选混合(QDII)人民币A</t>
+          <t>易方达中证家电龙头ETF联接发起式C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>561.84</v>
+        <v>293.21</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6019</v>
+        <v>1.3642</v>
       </c>
       <c r="E9" t="n">
-        <v>900.01</v>
+        <v>400</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1549,13 +1304,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>529.4400000000001</v>
+        <v>251.77</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3222</v>
+        <v>1.5887</v>
       </c>
       <c r="E10" t="n">
-        <v>700.02</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1575,22 +1330,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>012769</t>
+          <t>024203</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华夏中证动漫游戏ETF发起式联接C</t>
+          <t>永赢制造升级智选混合发起C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>472.84</v>
+        <v>254.3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4804</v>
+        <v>1.2713</v>
       </c>
       <c r="E11" t="n">
-        <v>699.99</v>
+        <v>323.29</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1610,22 +1365,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>007280</t>
+          <t>016387</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>摩根日本精选股票(QDII)A</t>
+          <t>永赢低碳环保智选混合发起C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>380.65</v>
+        <v>284.91</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8389</v>
+        <v>0.8192</v>
       </c>
       <c r="E12" t="n">
-        <v>699.98</v>
+        <v>233.39</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1645,22 +1400,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012725</t>
+          <t>002834</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>国泰中证畜牧养殖ETF联接C</t>
+          <t>华夏新锦绣混合C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>766.29</v>
+        <v>64.64</v>
       </c>
       <c r="D13" t="n">
-        <v>0.783</v>
+        <v>3.0941</v>
       </c>
       <c r="E13" t="n">
-        <v>600.03</v>
+        <v>200</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1680,22 +1435,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>018897</t>
+          <t>004744</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>易方达消费电子ETF联接C</t>
+          <t>易方达创业板ETF联接C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>312.6</v>
+        <v>31.58</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8127</v>
+        <v>3.1662</v>
       </c>
       <c r="E14" t="n">
-        <v>566.65</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1715,22 +1470,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>015945</t>
+          <t>021172</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>易方达国防军工混合C</t>
+          <t>华安北证50成份指数发起式A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>274.04</v>
+        <v>51.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4596</v>
+        <v>1.9251</v>
       </c>
       <c r="E15" t="n">
-        <v>399.99</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1750,22 +1505,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015897</t>
+          <t>001595</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天弘中证细分化工产业主题ETF联接C</t>
+          <t>天弘中证银行ETF联接C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>375.32</v>
+        <v>57.75</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7993</v>
+        <v>1.7317</v>
       </c>
       <c r="E16" t="n">
-        <v>300.01</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1785,22 +1540,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>011103</t>
+          <t>022365</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>天弘中证光伏产业指数C</t>
+          <t>永赢科技智选混合发起C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>248.92</v>
+        <v>35.79</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8035</v>
+        <v>2.7353</v>
       </c>
       <c r="E17" t="n">
-        <v>200</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1814,41 +1569,6 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>000834</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>大成纳斯达克100ETF联接(QDII)A</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>17.66</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5.3473</v>
-      </c>
-      <c r="E18" t="n">
-        <v>94.43000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
         <v>1</v>
       </c>
     </row>
